--- a/daily_matches/job_matches_2026-06-27.xlsx
+++ b/daily_matches/job_matches_2026-06-27.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Engineering</t>
+          <t>Senior Software Engineer - Platform</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Resmed</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git, Databricks, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db8f881d56beb45b</t>
+          <t>https://www.indeed.com/viewjob?jk=3ecc89ba914fc587</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Sr. IT Big Data Developer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, Cassandra</t>
+          <t>Data Scientist, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69e822c1cf66e308</t>
+          <t>https://www.indeed.com/viewjob?jk=dba4bfa4195a614f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, Cassandra</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37dbcc8bf6973335</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0b8be0e4857da6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>AI Systems Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Suffolk Construction</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, Cassandra</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, Prompt Engineering, Databricks, Kafka, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d84fecedb12dd363</t>
+          <t>https://www.indeed.com/viewjob?jk=c00f3c6eabf7aab0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer 2 - Full Stack</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, MongoDB, Cassandra</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, FastAPI, CI/CD, Git, Hadoop</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abe999fc3b54fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=da83aa2cd6ded06b</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect – Washington, DC</t>
+          <t>Python AI Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Creative Information Technology India</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Falls Church, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python</t>
+          <t>AI Engineer, RAG, TensorFlow, FastAPI, Docker, CI/CD, Jenkins, Git, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94d5786e7c110147</t>
+          <t>https://www.indeed.com/viewjob?jk=277d01c969e4d645</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sustainability Data and AI Consultant</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>PPG</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Gemini, TensorFlow, PyTorch, Data Lake, Git, Snowflake, Databricks, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, AWS SageMaker, GCP Vertex AI, Azure ML, Git, Databricks, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,59 +706,59 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc927e4fc5649b27</t>
+          <t>https://www.indeed.com/viewjob?jk=fd5acf2d842048a4</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer- IT AI II USA</t>
+          <t>Marketing Data Scientist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>First Solar</t>
+          <t>iProcess Solutions Inc</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Perrysburg, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, Pinecone, Prompt Engineering, Synapse, FastAPI, Docker, CI/CD, Git, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, XGBoost, LightGBM, CatBoost, Git, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=210ba3facdfb1efd</t>
+          <t>https://www.indeed.com/viewjob?jk=13dfcf04d247c531</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Contract Associate Engineer, Software Development</t>
+          <t>Sr Data Scientist - Member Growth &amp; Prescreen Modeling</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Sinclair Broadcast Group</t>
+          <t>BECU</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Tukwila, WA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, MySQL, MongoDB, Python</t>
+          <t>Data Scientist, Redshift, BigQuery, MLflow, Snowflake, BigQuery, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d314b4267c96919</t>
+          <t>https://www.indeed.com/viewjob?jk=93bbd48d3322e5c7</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior IT Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Edwards Lifesciences</t>
+          <t>Diverse Agile Solutions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S3, EC2, CI/CD, GitHub Actions, Git, Databricks, PySpark, Python, SQL, R</t>
+          <t>Data Lake, Apache Airflow, CI/CD, Git, Snowflake, PostgreSQL, MySQL, NoSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02a96598db050be0</t>
+          <t>https://www.indeed.com/viewjob?jk=445f550d4f69a7c6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Scientist II</t>
+          <t>Senior Engineer, Invest Tech</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Axle</t>
+          <t>Invesco</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, EC2, Data Lake, Git, Snowflake, Databricks, Python, R</t>
+          <t>Copilot, S3, CI/CD, Git, Snowflake, Kafka, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b8f3bc9f90679fa</t>
+          <t>https://www.indeed.com/viewjob?jk=efdcc6d0c28ecda9</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI/ML Developer</t>
+          <t>Sr. AI/ML Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dassault Systèmes</t>
+          <t>HealthStream</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, LangChain, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Git, MySQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fbad5ab551a7d9e</t>
+          <t>https://www.indeed.com/viewjob?jk=450a1ed4e2dc5557</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Sr Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>EBSCO Information Services</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Vance, AL, US USA</t>
+          <t>Ipswich, MA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Git, Databricks, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, S3, EC2, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc97c8418742f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c356bd682ddb52</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer I</t>
+          <t>Junior Analytics Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>SewerAI</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, Apache Airflow, Git, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>S3, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=780ce104b6245201</t>
+          <t>https://www.indeed.com/viewjob?jk=ef23c8da578678cc</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer I</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chagrin Falls, OH, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, Apache Airflow, Git, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>Data Scientist, RAG, MLflow, CI/CD, Git, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2252a7a3c634ef72</t>
+          <t>https://www.indeed.com/viewjob?jk=8122e2600ab1407a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Warehouse Software Engineer I</t>
+          <t>Security Platform Engineer 2 (Hybrid - Seattle)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Babel Street</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Somerville, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>BigQuery, Data Lake, Apache Airflow, Git, BigQuery, Tableau, Python, SQL, R, Optimization</t>
+          <t>RAG, Copilot, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c09010afa53983f</t>
+          <t>https://www.indeed.com/viewjob?jk=49744f4cb7f46ca9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Analyst Sfty Data Governance &amp; Insights</t>
+          <t>Software Engineering PMTS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>JetBlue</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Long Island City, NY, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Git, Snowflake, Tableau, Python, SQL, R, Scala</t>
+          <t>Copilot, Prompt Engineering, Docker, Kubernetes, Terraform, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f2890396bc01fe5</t>
+          <t>https://www.indeed.com/viewjob?jk=ddd05fa6f8801fb4</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Scientist / Software Engineer Intern</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cvent</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Menlo Park, CA, US USA</t>
+          <t>Tysons Corner, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Scientist, Copilot, FastAPI, Git, PostgreSQL, Python, SQL, R, Java</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, MongoDB, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,112 +1091,567 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba1872074018c2c</t>
+          <t>https://www.indeed.com/viewjob?jk=3842f995b4aebd91</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Research Engineer – Machine Learning &amp; Robotics</t>
+          <t>Postdoctoral Researcher</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Jumio</t>
+          <t>University of Utah</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lenexa, KS, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, S3, EC2, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, MongoDB, SQL, R</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed6b6bcb700580f8</t>
+          <t>https://www.indeed.com/viewjob?jk=eade18fd1429abee</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior ML Engineer, Computer Vision - Applied AI</t>
+          <t>Python Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Uber</t>
+          <t>Altumint</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lanham, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Gemini, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, FastAPI, Docker, CI/CD, Jenkins, GitHub Actions, Git, PostgreSQL, Python, SQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08f893cdc0da39ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e881184c7943aa42</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Software Development Engineer</t>
+          <t>Data Platform Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>MetLife</t>
+          <t>SS&amp;C</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cary, NC, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>RAG, Kubernetes, Apache Airflow, CI/CD, Git, Kafka, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a25c9133cd0e70a2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Toyota North America</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, PyTorch, AWS SageMaker, Azure ML, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=967be8496cfd1730</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Strategic DevSecOps Consultant</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>CloudBees Inc</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=823149af7afd6104</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Java Spark Developer-Software Engineer II</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10024b0b6c83d565</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Software Engineer III - Senior Java Spark Developer</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bdb63c2981f40a27</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Engineer III</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Visual Comfort &amp; Co</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Houston, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Copilot, Azure ML, Synapse, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ed6f23c724c8deb1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Senior Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
         <v>10</v>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Generative AI, Prompt Engineering, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f99513aab38f1401</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, BigQuery, Dataflow, CI/CD, Terraform, BigQuery, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=da5ecf3dafaf449a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Mercola</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cape Coral, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e77fb5d68f5dbd13</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Full Stack Developer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Mercola</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2e00b798cd905b2d</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>El Pollo Loco</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, CI/CD, Terraform, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8bd72bf197f82e23</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Software Engineer II, Ad Engineering</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>The Washington Post</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>RAG, S3, EC2, Docker, CI/CD, Jenkins, Git, R, Java</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b0d0f55ff7b22862</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Full Stack Software Engineer III - Network Perimeter &amp; CDN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, CI/CD, Terraform, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26a74819fe5bfadf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Applied Scientist</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Generative AI, TensorFlow, PyTorch, Keras, OpenCV, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc539bb877c770d9</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Scientist Senior Associate - Digital Platforms</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, Git, Snowflake, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5456b6f33aef382a</t>
         </is>
       </c>
     </row>
